--- a/mapping/PDTD_DTM/Mapping_FCT_CLOS_APPLICATION.xlsx
+++ b/mapping/PDTD_DTM/Mapping_FCT_CLOS_APPLICATION.xlsx
@@ -411,8 +411,8 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -718,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>Fact hồ sơ tín dụng CLOS tại PDTD_DTM, relay 1:1 các cột gốc từ STG_DTM.STG_FCT_CLOS_APPLICATION, bổ sung user xử lý từng bước, cờ carry-forward tiến trình, business rule trạng thái/auto-cancel, người đại diện pháp lý, và tra cứu SLA/luồng nghiệp vụ</t>
+          <t>Bảng FACT xương sống của CLOS tại PDTD_DTM — bê nguyên 1:1 phần lớn cột từ STG_DTM.STG_FCT_CLOS_APPLICATION, bổ sung các khóa kỹ thuật T24, user theo bước, SLA, cờ carry-forward</t>
         </is>
       </c>
       <c r="E2" s="52" t="inlineStr">
@@ -802,7 +802,7 @@
       <c r="A5" s="13" t="n"/>
       <c r="E5" s="52" t="inlineStr">
         <is>
-          <t>STG_DIM_CLOS_WORKSTEP_DECISION AS E2</t>
+          <t>Q_RLOS_REF_WORKSTEP_2SYSTEMS AS E</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       <c r="A6" s="13" t="n"/>
       <c r="E6" s="52" t="inlineStr">
         <is>
-          <t>Q_RLOS_REF_WORKSTEP_2SYSTEMS AS F</t>
+          <t>STG_DIM_CLOS_WORKSTEP_DECISION AS F</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       <c r="A7" s="13" t="n"/>
       <c r="E7" s="52" t="inlineStr">
         <is>
-          <t>STG_DIM_CLOS_PRODUCT PL AS G</t>
+          <t>STG_DIM_CLOS_PRODUCT AS PL/SP (2 lần join, layer Product Line/Sub Product)</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       <c r="A8" s="13" t="n"/>
       <c r="E8" s="52" t="inlineStr">
         <is>
-          <t>STG_DIM_CLOS_PRODUCT SP AS H</t>
+          <t>STG_DIM_CLOS_APPLICATION AS I</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       <c r="A9" s="13" t="n"/>
       <c r="E9" s="53" t="inlineStr">
         <is>
-          <t>STG_DIM_CLOS_APPLICATION AS I</t>
+          <t>CLOS_REF_SLA_TDKHDNL AS J</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       <c r="A10" s="13" t="n"/>
       <c r="E10" s="53" t="inlineStr">
         <is>
-          <t>CLOS_REF_SLA_TDKHDNL AS J</t>
+          <t>CLOS_REF_SLA_TDKHDN AS K</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       <c r="A11" s="13" t="n"/>
       <c r="E11" s="53" t="inlineStr">
         <is>
-          <t>CLOS_REF_SLA_TDKHDN AS K</t>
+          <t>STG_FCT_CLOS_LEGAL_PARTY AS L</t>
         </is>
       </c>
     </row>
@@ -858,17 +858,13 @@
       <c r="A12" s="13" t="n"/>
       <c r="E12" s="53" t="inlineStr">
         <is>
-          <t>STG_FCT_CLOS_LEGAL_PARTY AS L</t>
+          <t>FCT_CLOS_APPLICATION_PREV AS M (alias p)</t>
         </is>
       </c>
     </row>
     <row r="13" hidden="1">
       <c r="A13" s="13" t="n"/>
-      <c r="E13" s="53" t="inlineStr">
-        <is>
-          <t>FCT_CLOS_APPLICATION_PREV AS M</t>
-        </is>
-      </c>
+      <c r="E13" s="53" t="n"/>
     </row>
     <row r="14" hidden="1">
       <c r="A14" s="13" t="n"/>
@@ -952,7 +948,7 @@
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới hồ sơ tín dụng</t>
+          <t>Khóa hồ sơ tín dụng</t>
         </is>
       </c>
       <c r="D18" s="54" t="inlineStr">
@@ -966,199 +962,199 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="15" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
         <is>
-          <t>WORKSTEP_DECISION_SK</t>
+          <t>WI_NAME</t>
         </is>
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới bước xử lý - quyết định</t>
+          <t>Mã hồ sơ tín dụng</t>
         </is>
       </c>
       <c r="D19" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_CLOS_WORKSTEP_DECISION. Mặc định -1 — đổi tên từ LAST_WORKSTEP_DECISION_SK</t>
+          <t>PK (2/2) — Mã hồ sơ tín dụng CLOS</t>
         </is>
       </c>
       <c r="E19" s="31" t="inlineStr">
         <is>
-          <t>A.WORKSTEP_DECISION_SK</t>
+          <t>A.WI_NAME</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="28" t="inlineStr">
         <is>
+          <t>WORKSTEP_DECISION_SK</t>
+        </is>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Khóa bước &amp; quyết định</t>
+        </is>
+      </c>
+      <c r="D20" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_CLOS_WORKSTEP_DECISION. Mặc định -1 — đổi tên từ LAST_WORKSTEP_DECISION_SK</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
+        <is>
+          <t>A.WORKSTEP_DECISION_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>WORKSTEP_CODE</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Mã bước xử lý cuối</t>
+        </is>
+      </c>
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK, 1 phần BK composite của DIM_CLOS_WORKSTEP_DECISION, giá trị đã có sẵn trong bước lookup WORKSTEP_DECISION_SK</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>A.WORKSTEP_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>DECISION_CODE</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Mã quyết định cuối</t>
+        </is>
+      </c>
+      <c r="D22" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — nửa còn lại BK composite của DIM_CLOS_WORKSTEP_DECISION, giá trị đã có sẵn trong bước lookup WORKSTEP_DECISION_SK</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>A.DECISION_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
           <t>PRODUCTLINE_SK</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới nhóm sản phẩm</t>
-        </is>
-      </c>
-      <c r="D20" s="54" t="inlineStr">
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Khóa dòng sản phẩm</t>
+        </is>
+      </c>
+      <c r="D23" s="54" t="inlineStr">
         <is>
           <t>Khóa tới DIM_CLOS_PRODUCT (layer Product Line). Mặc định -1 nếu không khớp</t>
         </is>
       </c>
-      <c r="E20" s="31" t="inlineStr">
+      <c r="E23" s="31" t="inlineStr">
         <is>
           <t>A.PRODUCTLINE_SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="28" t="inlineStr">
-        <is>
-          <t>SUB_PRODUCT_SK</t>
-        </is>
-      </c>
-      <c r="B21" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới sản phẩm vay chi tiết</t>
-        </is>
-      </c>
-      <c r="D21" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_CLOS_PRODUCT (layer Sub Product). Mặc định -1 nếu không khớp</t>
-        </is>
-      </c>
-      <c r="E21" s="31" t="inlineStr">
-        <is>
-          <t>A.SUB_PRODUCT_SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="28" t="inlineStr">
-        <is>
-          <t>COMPANY_SK</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới công ty/tổ chức</t>
-        </is>
-      </c>
-      <c r="D22" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_LOS_COMPANY. Mặc định -1 nếu không khớp</t>
-        </is>
-      </c>
-      <c r="E22" s="31" t="inlineStr">
-        <is>
-          <t>A.COMPANY_SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>CUSTOMER_SK</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="C23" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới khách hàng LOS</t>
-        </is>
-      </c>
-      <c r="D23" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_CLOS_CUSTOMER — quan hệ 1:1 với hồ sơ qua WI_NAME. Mặc định -1 nếu không khớp. Đây là chân khách hàng LOS — khác T24_CUSTOMER_SK (chân T24)</t>
-        </is>
-      </c>
-      <c r="E23" s="31" t="inlineStr">
-        <is>
-          <t>A.CUSTOMER_SK</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
         <is>
-          <t>T24_CUSTOMER_SK</t>
+          <t>PRODUCTLINE_CODE</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Mã dòng sản phẩm</t>
+        </is>
+      </c>
+      <c r="D24" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK (layer Product Line), giá trị đã có sẵn trong bước lookup PRODUCTLINE_SK</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>A.PRODUCTLINE_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>SUB_PRODUCT_SK</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới khách hàng T24</t>
-        </is>
-      </c>
-      <c r="D24" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_T24_CUSTOMER (T24). Mặc định -1 nếu không khớp</t>
-        </is>
-      </c>
-      <c r="E24" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN B ON B.DIMENSION_KEY = A.CUSTOMER_SK → LEFT JOIN C ON C.LEGAL_ID = B.CUSTOMER_CODE → C.DIMENSION_KEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>WI_NAME</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Mã hồ sơ tín dụng</t>
+          <t>Khóa sản phẩm nhánh</t>
         </is>
       </c>
       <c r="D25" s="54" t="inlineStr">
         <is>
-          <t>PK (2/2) — Mã hồ sơ tín dụng CLOS</t>
+          <t>Khóa tới DIM_CLOS_PRODUCT (layer Sub Product). Mặc định -1 nếu không khớp</t>
         </is>
       </c>
       <c r="E25" s="31" t="inlineStr">
         <is>
-          <t>A.WI_NAME</t>
+          <t>A.SUB_PRODUCT_SK</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>RI_USER</t>
+          <t>SUB_PRODUCT_CODE</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
@@ -1168,1433 +1164,1918 @@
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>User khởi tạo hồ sơ</t>
+          <t>Mã sản phẩm nhánh</t>
         </is>
       </c>
       <c r="D26" s="54" t="inlineStr">
         <is>
-          <t>User khởi tạo hồ sơ (bước RequestInitiate) — PHÁI SINH TẠI PDTD_DTM</t>
+          <t>CỘT MỚI — BK thật cạnh SK (layer Sub Product, UNIQUE toàn cục), giá trị đã có sẵn trong bước lookup SUB_PRODUCT_SK</t>
         </is>
       </c>
       <c r="E26" s="31" t="inlineStr">
         <is>
-          <t>(SELECT D.USERNAME FROM D WHERE D.WORKSTEP_CODE = 'RequestInitiate' AND D.WI_NAME = A.WI_NAME)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="45" customHeight="1">
+          <t>A.SUB_PRODUCT_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>BRANCH_USER</t>
+          <t>COMPANY_SK</t>
         </is>
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(100)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>User xử lý bước BranchSupport</t>
+          <t>Khóa đơn vị kinh doanh</t>
         </is>
       </c>
       <c r="D27" s="54" t="inlineStr">
         <is>
-          <t>User xử lý bước BranchSupport, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
+          <t>Khóa tới DIM_LOS_COMPANY. Mặc định -1 nếu không khớp</t>
         </is>
       </c>
       <c r="E27" s="31" t="inlineStr">
         <is>
-          <t>(SELECT D.USERNAME FROM D WHERE D.WORKSTEP_CODE = 'BranchSupport' AND D.WI_NAME = A.WI_NAME ORDER BY D.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="45" customHeight="1">
+          <t>A.COMPANY_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
         <is>
-          <t>DDE_USER</t>
+          <t>COMPANY_CODE</t>
         </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(100)</t>
+          <t>VARCHAR2(50)</t>
         </is>
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>User xử lý bước DetailDataEntry</t>
+          <t>Mã đơn vị kinh doanh</t>
         </is>
       </c>
       <c r="D28" s="54" t="inlineStr">
         <is>
-          <t>User xử lý bước DetailDataEntry, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
+          <t>CỘT MỚI — BK cạnh SK (layer Company), cùng giá trị đã dùng để lookup COMPANY_SK</t>
         </is>
       </c>
       <c r="E28" s="31" t="inlineStr">
         <is>
-          <t>(SELECT D.USERNAME FROM D WHERE D.WORKSTEP_CODE = 'DetailDataEntry' AND D.WI_NAME = A.WI_NAME ORDER BY D.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+          <t>A.COMPANY_CODE</t>
         </is>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1">
       <c r="A29" s="28" t="inlineStr">
         <is>
+          <t>CUSTOMER_SK</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>Khóa khách hàng</t>
+        </is>
+      </c>
+      <c r="D29" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_CLOS_CUSTOMER — quan hệ 1:1 với hồ sơ qua WI_NAME. Mặc định -1 nếu không khớp. Đây là chân khách hàng LOS — khác T24_CUSTOMER_SK (chân T24, bổ sung riêng tại PDTD_DTM)</t>
+        </is>
+      </c>
+      <c r="E29" s="31" t="inlineStr">
+        <is>
+          <t>A.CUSTOMER_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CODE</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Mã khách hàng</t>
+        </is>
+      </c>
+      <c r="D30" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK (DIM_CLOS_CUSTOMER), giá trị đã tra ra trong bước lookup CUSTOMER_SK</t>
+        </is>
+      </c>
+      <c r="E30" s="31" t="inlineStr">
+        <is>
+          <t>A.CUSTOMER_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>T24_CUSTOMER_SK</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>Khóa khách hàng T24</t>
+        </is>
+      </c>
+      <c r="D31" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_T24_CUSTOMER (T24), tra qua ORG_LEGAL_ID trên DIM_CLOS_CUSTOMER. Mặc định -1</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
+        <is>
+          <t>C.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>T24_CUSTOMER_CODE</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(50)</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>Mã khách hàng T24</t>
+        </is>
+      </c>
+      <c r="D32" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK, mã khách hàng T24, giá trị đã có sẵn trong bước lookup T24_CUSTOMER_SK</t>
+        </is>
+      </c>
+      <c r="E32" s="31" t="inlineStr">
+        <is>
+          <t>C.CUSTOMER</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>RI_USER</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>User khởi tạo hồ sơ</t>
+        </is>
+      </c>
+      <c r="D33" s="54" t="inlineStr">
+        <is>
+          <t>User khởi tạo hồ sơ (bước RequestInitiate) — PHÁI SINH TẠI PDTD_DTM: USERNAME tại bản ghi D WHERE WORKSTEP_CODE='RequestInitiate' theo WI_NAME (quy ước tối đa 1 dòng/hồ sơ, không cần MAX/MIN EXITDATE)</t>
+        </is>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
+        <is>
+          <t>N1.USERNAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>BRANCH_USER</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>User Chi nhánh</t>
+        </is>
+      </c>
+      <c r="D34" s="54" t="inlineStr">
+        <is>
+          <t>User xử lý bước BranchSupport, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
+        </is>
+      </c>
+      <c r="E34" s="31" t="inlineStr">
+        <is>
+          <t>N2.USERNAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>DDE_USER</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>User Chuyên viên nhập liệu</t>
+        </is>
+      </c>
+      <c r="D35" s="54" t="inlineStr">
+        <is>
+          <t>User xử lý bước DetailDataEntry, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
+        </is>
+      </c>
+      <c r="E35" s="31" t="inlineStr">
+        <is>
+          <t>N3.USERNAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
           <t>QC_USER</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B36" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>User xử lý bước DataInputerChecker</t>
-        </is>
-      </c>
-      <c r="D29" s="54" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>User Kiểm soát nhập liệu</t>
+        </is>
+      </c>
+      <c r="D36" s="54" t="inlineStr">
         <is>
           <t>User xử lý bước DataInputerChecker, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
-      <c r="E29" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT D.USERNAME FROM D WHERE D.WORKSTEP_CODE = 'DataInputerChecker' AND D.WI_NAME = A.WI_NAME ORDER BY D.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="28" t="inlineStr">
-        <is>
-          <t>UND_MAKER_USER</t>
-        </is>
-      </c>
-      <c r="B30" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C30" s="26" t="inlineStr">
-        <is>
-          <t>User xử lý bước UnderwriterMaker</t>
-        </is>
-      </c>
-      <c r="D30" s="54" t="inlineStr">
-        <is>
-          <t>User xử lý bước UnderwriterMaker, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E30" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT D.USERNAME FROM D WHERE D.WORKSTEP_CODE = 'UnderwriterMaker' AND D.WI_NAME = A.WI_NAME ORDER BY D.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="45" customHeight="1">
-      <c r="A31" s="28" t="inlineStr">
-        <is>
-          <t>UND_CHECKER_USER</t>
-        </is>
-      </c>
-      <c r="B31" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>User xử lý bước UnderwriterChecker</t>
-        </is>
-      </c>
-      <c r="D31" s="54" t="inlineStr">
-        <is>
-          <t>User xử lý bước UnderwriterChecker, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E31" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT D.USERNAME FROM D WHERE D.WORKSTEP_CODE = 'UnderwriterChecker' AND D.WI_NAME = A.WI_NAME ORDER BY D.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="45" customHeight="1">
-      <c r="A32" s="28" t="inlineStr">
-        <is>
-          <t>PHV_USER</t>
-        </is>
-      </c>
-      <c r="B32" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C32" s="26" t="inlineStr">
-        <is>
-          <t>User xử lý bước PhoneVerification</t>
-        </is>
-      </c>
-      <c r="D32" s="54" t="inlineStr">
-        <is>
-          <t>User xử lý bước PhoneVerification, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E32" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT D.USERNAME FROM D WHERE D.WORKSTEP_CODE = 'PhoneVerification' AND D.WI_NAME = A.WI_NAME ORDER BY D.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="45" customHeight="1">
-      <c r="A33" s="28" t="inlineStr">
-        <is>
-          <t>FA_USER</t>
-        </is>
-      </c>
-      <c r="B33" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C33" s="26" t="inlineStr">
-        <is>
-          <t>User Chuyên viên Thực địa</t>
-        </is>
-      </c>
-      <c r="D33" s="54" t="inlineStr">
-        <is>
-          <t>User Chuyên viên Thực địa — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E33" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT D.USERNAME FROM D WHERE D.WORKSTEP_CODE = 'FieldAssessment' AND D.WI_NAME = A.WI_NAME ORDER BY D.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customHeight="1">
-      <c r="A34" s="28" t="inlineStr">
-        <is>
-          <t>APPROVER_USER</t>
-        </is>
-      </c>
-      <c r="B34" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C34" s="26" t="inlineStr">
-        <is>
-          <t>User xử lý bước CreditApproval</t>
-        </is>
-      </c>
-      <c r="D34" s="54" t="inlineStr">
-        <is>
-          <t>User xử lý bước CreditApproval, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E34" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT D.USERNAME FROM D WHERE D.WORKSTEP_CODE = 'CreditApproval' AND D.WI_NAME = A.WI_NAME ORDER BY D.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="45" customHeight="1">
-      <c r="A35" s="28" t="inlineStr">
-        <is>
-          <t>COMMITTEE_USER</t>
-        </is>
-      </c>
-      <c r="B35" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C35" s="26" t="inlineStr">
-        <is>
-          <t>User Hội đồng tín dụng</t>
-        </is>
-      </c>
-      <c r="D35" s="54" t="inlineStr">
-        <is>
-          <t>User Hội đồng tín dụng — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E35" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT D.USERNAME FROM D WHERE D.WORKSTEP_CODE = 'CreditCommittee' AND D.WI_NAME = A.WI_NAME ORDER BY D.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="45" customHeight="1">
-      <c r="A36" s="28" t="inlineStr">
-        <is>
-          <t>HOS_USER</t>
-        </is>
-      </c>
-      <c r="B36" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C36" s="26" t="inlineStr">
-        <is>
-          <t>User Hỗ trợ phê duyệt</t>
-        </is>
-      </c>
-      <c r="D36" s="54" t="inlineStr">
-        <is>
-          <t>User Hỗ trợ phê duyệt — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
       <c r="E36" s="31" t="inlineStr">
         <is>
-          <t>(SELECT D.USERNAME FROM D WHERE D.WORKSTEP_CODE = 'HOSupport' AND D.WI_NAME = A.WI_NAME ORDER BY D.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+          <t>N4.USERNAME</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="28" t="inlineStr">
         <is>
-          <t>PROCESSED_DATE</t>
+          <t>UND_MAKER_USER</t>
         </is>
       </c>
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C37" s="26" t="inlineStr">
         <is>
-          <t>Ngày xử lý</t>
+          <t>User Chuyên viên thẩm định</t>
         </is>
       </c>
       <c r="D37" s="54" t="inlineStr">
         <is>
-          <t>Ngày xử lý chung của hồ sơ theo 3 mức ưu tiên (phê duyệt cuối / hủy / hoàn tất gần nhất)</t>
+          <t>User xử lý bước UnderwriterMaker, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
       <c r="E37" s="31" t="inlineStr">
         <is>
-          <t>A.PROCESSED_DATE</t>
+          <t>N5.USERNAME</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="28" t="inlineStr">
         <is>
-          <t>LAST_APPROVAL_DATE</t>
+          <t>UND_CHECKER_USER</t>
         </is>
       </c>
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C38" s="26" t="inlineStr">
         <is>
-          <t>Ngày phê duyệt gần nhất</t>
+          <t>User Kiểm soát thẩm định</t>
         </is>
       </c>
       <c r="D38" s="54" t="inlineStr">
         <is>
-          <t>MAX(EXITDATE) tại bước phê duyệt (không lọc DECISION) — PHÁI SINH TẠI PDTD_DTM</t>
+          <t>User xử lý bước UnderwriterChecker, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
       <c r="E38" s="31" t="inlineStr">
         <is>
-          <t>(SELECT MAX(D.EXITDATE) FROM D WHERE D.WORKSTEP_CODE IN ('CreditApproval','CreditCommittee') AND D.WI_NAME = A.WI_NAME)</t>
+          <t>N6.USERNAME</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="28" t="inlineStr">
         <is>
-          <t>MIN_UWM</t>
+          <t>PHV_USER</t>
         </is>
       </c>
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C39" s="26" t="inlineStr">
         <is>
-          <t>Thời điểm bắt đầu UnderwriterMaker sớm nhất</t>
+          <t>User Chuyên viên Thẩm định điện thoại</t>
         </is>
       </c>
       <c r="D39" s="54" t="inlineStr">
         <is>
-          <t>MIN(ENTRYDATE) tại UnderwriterMaker — PHÁI SINH TẠI PDTD_DTM</t>
+          <t>User xử lý bước PhoneVerification, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
       <c r="E39" s="31" t="inlineStr">
         <is>
-          <t>(SELECT MIN(D.ENTRYDATE) FROM D WHERE D.WORKSTEP_CODE = 'UnderwriterMaker' AND D.WI_NAME = A.WI_NAME)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
+          <t>N7.USERNAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
       <c r="A40" s="28" t="inlineStr">
         <is>
-          <t>MIN_APP</t>
+          <t>FA_USER</t>
         </is>
       </c>
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C40" s="26" t="inlineStr">
         <is>
-          <t>Thời điểm bắt đầu phê duyệt sớm nhất</t>
+          <t>User Chuyên viên Thực địa</t>
         </is>
       </c>
       <c r="D40" s="54" t="inlineStr">
         <is>
-          <t>MIN(ENTRYDATE) tại CreditApproval/CreditCommittee — PHÁI SINH TẠI PDTD_DTM</t>
+          <t>User Chuyên viên Thực địa — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
       <c r="E40" s="31" t="inlineStr">
         <is>
-          <t>(SELECT MIN(D.ENTRYDATE) FROM D WHERE D.WORKSTEP_CODE IN ('CreditApproval','CreditCommittee') AND D.WI_NAME = A.WI_NAME)</t>
+          <t>N8.USERNAME</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="28" t="inlineStr">
         <is>
+          <t>APPROVER_USER</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>User Chuyên gia phê duyệt</t>
+        </is>
+      </c>
+      <c r="D41" s="54" t="inlineStr">
+        <is>
+          <t>User xử lý bước CreditApproval, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
+        </is>
+      </c>
+      <c r="E41" s="31" t="inlineStr">
+        <is>
+          <t>N9.USERNAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="28" t="inlineStr">
+        <is>
+          <t>COMMITTEE_USER</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>User Hội đồng tín dụng</t>
+        </is>
+      </c>
+      <c r="D42" s="54" t="inlineStr">
+        <is>
+          <t>User Hội đồng tín dụng — PHÁI SINH TẠI PDTD_DTM</t>
+        </is>
+      </c>
+      <c r="E42" s="31" t="inlineStr">
+        <is>
+          <t>N10.USERNAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="28" t="inlineStr">
+        <is>
+          <t>HOS_USER</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>User Hỗ trợ phê duyệt</t>
+        </is>
+      </c>
+      <c r="D43" s="54" t="inlineStr">
+        <is>
+          <t>User Hỗ trợ phê duyệt — PHÁI SINH TẠI PDTD_DTM</t>
+        </is>
+      </c>
+      <c r="E43" s="31" t="inlineStr">
+        <is>
+          <t>N11.USERNAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="28" t="inlineStr">
+        <is>
+          <t>PROCESSED_DATE</t>
+        </is>
+      </c>
+      <c r="B44" s="25" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>Ngày xử lý hồ sơ</t>
+        </is>
+      </c>
+      <c r="D44" s="54" t="inlineStr">
+        <is>
+          <t>Ngày xử lý chung của hồ sơ theo 3 mức ưu tiên (phê duyệt cuối / hủy / hoàn tất gần nhất)</t>
+        </is>
+      </c>
+      <c r="E44" s="31" t="inlineStr">
+        <is>
+          <t>A.PROCESSED_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="28" t="inlineStr">
+        <is>
+          <t>LAST_APPROVAL_DATE</t>
+        </is>
+      </c>
+      <c r="B45" s="25" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>Thời gian phê duyệt cuối</t>
+        </is>
+      </c>
+      <c r="D45" s="54" t="inlineStr">
+        <is>
+          <t>MAX(EXITDATE) tại bước phê duyệt (nhóm quyết định đã định nghĩa) — PHÁI SINH TẠI PDTD_DTM</t>
+        </is>
+      </c>
+      <c r="E45" s="31" t="inlineStr">
+        <is>
+          <t>N12.LAST_APPROVAL_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="28" t="inlineStr">
+        <is>
+          <t>MIN_UWM</t>
+        </is>
+      </c>
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>Thời gian hồ sơ lên CV thẩm định</t>
+        </is>
+      </c>
+      <c r="D46" s="54" t="inlineStr">
+        <is>
+          <t>MIN(ENTRYDATE) tại UnderwriterMaker — PHÁI SINH TẠI PDTD_DTM</t>
+        </is>
+      </c>
+      <c r="E46" s="31" t="inlineStr">
+        <is>
+          <t>N13.MIN_UWM</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="28" t="inlineStr">
+        <is>
+          <t>MIN_APP</t>
+        </is>
+      </c>
+      <c r="B47" s="25" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>Thời gian hồ sơ lên cấp phê duyệt</t>
+        </is>
+      </c>
+      <c r="D47" s="54" t="inlineStr">
+        <is>
+          <t>MIN(ENTRYDATE) tại CreditApproval/CreditCommittee — PHÁI SINH TẠI PDTD_DTM</t>
+        </is>
+      </c>
+      <c r="E47" s="31" t="inlineStr">
+        <is>
+          <t>N14.MIN_APP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="45" customHeight="1">
+      <c r="A48" s="28" t="inlineStr">
+        <is>
           <t>CANCEL_DATE</t>
         </is>
       </c>
-      <c r="B41" s="25" t="inlineStr">
+      <c r="B48" s="25" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C41" s="26" t="inlineStr">
-        <is>
-          <t>Ngày hủy hồ sơ</t>
-        </is>
-      </c>
-      <c r="D41" s="54" t="inlineStr">
-        <is>
-          <t>ENTRYDATE tại bước CancelRevoke — PHÁI SINH TẠI PDTD_DTM. FLAG_AUTO_CANCEL (cùng bảng) dùng input từ cột này</t>
-        </is>
-      </c>
-      <c r="E41" s="31" t="inlineStr">
-        <is>
-          <t>D.ENTRYDATE WHERE D.WORKSTEP_CODE = 'CancelRevoke' AND D.WI_NAME = A.WI_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="45" customHeight="1">
-      <c r="A42" s="28" t="inlineStr">
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>Thời gian vào vùng CancelRevoke</t>
+        </is>
+      </c>
+      <c r="D48" s="54" t="inlineStr">
+        <is>
+          <t>ENTRYDATE tại bước CancelRevoke — PHÁI SINH TẠI PDTD_DTM. FLAG_AUTO_CANCEL (business rule dựa trên cột này) tiếp tục tính tại chính bảng này, nay dùng input từ cột đã derive cùng bảng</t>
+        </is>
+      </c>
+      <c r="E48" s="31" t="inlineStr">
+        <is>
+          <t>N15.ENTRYDATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="105" customHeight="1">
+      <c r="A49" s="28" t="inlineStr">
         <is>
           <t>LAST_ENTRYDATE</t>
         </is>
       </c>
-      <c r="B42" s="25" t="inlineStr">
+      <c r="B49" s="25" t="inlineStr">
         <is>
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="C42" s="26" t="inlineStr">
-        <is>
-          <t>Thời điểm vào bước gần nhất</t>
-        </is>
-      </c>
-      <c r="D42" s="54" t="inlineStr">
-        <is>
-          <t>ENTRYDATE của sự kiện hoàn tất gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E42" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT D.ENTRYDATE FROM D WHERE D.EXITDATE IS NOT NULL AND D.WI_NAME = A.WI_NAME ORDER BY D.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="45" customHeight="1">
-      <c r="A43" s="28" t="inlineStr">
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>Thời gian vào bước cuối</t>
+        </is>
+      </c>
+      <c r="D49" s="54" t="inlineStr">
+        <is>
+          <t>ENTRYDATE của sự kiện hoàn tất gần nhất — PHÁI SINH TẠI PDTD_DTM. [CẦN REVIEW] LLD viết filter ORDER BY ENTRYDATE DESC FETCH FIRST 1 ROW ONLY không kèm PARTITION BY WI_NAME — rewrite sang ROW_NUMBER() OVER (PARTITION BY WI_NAME ORDER BY ENTRYDATE DESC) = 1 trong sub-select để giữ đúng cardinality 1 dòng/hồ sơ (FETCH FIRST đơn thuần chỉ trả 1 dòng cho TOÀN BẢNG).</t>
+        </is>
+      </c>
+      <c r="E49" s="31" t="inlineStr">
+        <is>
+          <t>N16.ENTRYDATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="120" customHeight="1">
+      <c r="A50" s="28" t="inlineStr">
         <is>
           <t>LAST_EXITDATE</t>
         </is>
       </c>
-      <c r="B43" s="25" t="inlineStr">
+      <c r="B50" s="25" t="inlineStr">
         <is>
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="C43" s="26" t="inlineStr">
-        <is>
-          <t>Thời điểm ra bước gần nhất</t>
-        </is>
-      </c>
-      <c r="D43" s="54" t="inlineStr">
-        <is>
-          <t>EXITDATE của cùng sự kiện hoàn tất gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E43" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT D.EXITDATE FROM D WHERE D.EXITDATE IS NOT NULL AND D.WI_NAME = A.WI_NAME ORDER BY D.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="45" customHeight="1">
-      <c r="A44" s="28" t="inlineStr">
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>Thời gian kết thúc bước cuối</t>
+        </is>
+      </c>
+      <c r="D50" s="54" t="inlineStr">
+        <is>
+          <t>EXITDATE của cùng sự kiện hoàn tất gần nhất — PHÁI SINH TẠI PDTD_DTM, cùng bản ghi 'sự kiện hoàn tất gần nhất' (cột LAST_ENTRYDATE). [CẦN REVIEW] Cùng rewrite ROW_NUMBER()/PARTITION BY như LAST_ENTRYDATE — phải dùng đúng CÙNG 1 sub-select (cùng bản ghi) với LAST_ENTRYDATE/PRE_WORKSTEP_CODE/LAST_REMARKS, không phải 4 sub-select độc lập có thể chọn ra 4 bản ghi khác nhau nếu có đồng hạng ENTRYDATE.</t>
+        </is>
+      </c>
+      <c r="E50" s="31" t="inlineStr">
+        <is>
+          <t>N16.EXITDATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" s="28" t="inlineStr">
         <is>
           <t>PRE_WORKSTEP_CODE</t>
         </is>
       </c>
-      <c r="B44" s="25" t="inlineStr">
+      <c r="B51" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C44" s="26" t="inlineStr">
-        <is>
-          <t>Bước xử lý liền trước</t>
-        </is>
-      </c>
-      <c r="D44" s="54" t="inlineStr">
-        <is>
-          <t>Bước xử lý liền trước (LAG theo ENTRYDATE) của sự kiện hoàn tất gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E44" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT LAG(D.WORKSTEP_CODE) OVER (PARTITION BY D.WI_NAME ORDER BY D.ENTRYDATE) FROM D WHERE D.WI_NAME = A.WI_NAME AND D.EXITDATE IS NOT NULL ORDER BY D.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="45" customHeight="1">
-      <c r="A45" s="28" t="inlineStr">
+      <c r="C51" s="26" t="inlineStr">
+        <is>
+          <t>Bước hồ sơ trước đó</t>
+        </is>
+      </c>
+      <c r="D51" s="54" t="inlineStr">
+        <is>
+          <t>Bước xử lý liền trước (LAG theo ENTRYDATE) — PHÁI SINH TẠI PDTD_DTM : LAG(WORKSTEP_CODE) OVER (PARTITION BY WI_NAME ORDER BY ENTRYDATE) trên D của sự kiện hoàn tất gần nhất</t>
+        </is>
+      </c>
+      <c r="E51" s="31" t="inlineStr">
+        <is>
+          <t>LAG(D.WORKSTEP_CODE) OVER (PARTITION BY D.WI_NAME ORDER BY D.ENTRYDATE) WHERE D.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="75" customHeight="1">
+      <c r="A52" s="28" t="inlineStr">
         <is>
           <t>LAST_REMARKS</t>
         </is>
       </c>
-      <c r="B45" s="25" t="inlineStr">
+      <c r="B52" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(4000)</t>
         </is>
       </c>
-      <c r="C45" s="26" t="inlineStr">
-        <is>
-          <t>Ghi chú bước gần nhất</t>
-        </is>
-      </c>
-      <c r="D45" s="54" t="inlineStr">
-        <is>
-          <t>Ghi chú của sự kiện hoàn tất gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E45" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT D.REMARKS FROM D WHERE D.EXITDATE IS NOT NULL AND D.WI_NAME = A.WI_NAME ORDER BY D.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="28" t="inlineStr">
+      <c r="C52" s="26" t="inlineStr">
+        <is>
+          <t>Ghi chú ý kiến bước cuối</t>
+        </is>
+      </c>
+      <c r="D52" s="54" t="inlineStr">
+        <is>
+          <t>Ghi chú của sự kiện hoàn tất gần nhất — PHÁI SINH TẠI PDTD_DTM, cùng bản ghi 'sự kiện hoàn tất gần nhất' với LAST_ENTRYDATE/LAST_EXITDATE/PRE_WORKSTEP_CODE. [CẦN REVIEW] Cùng rewrite ROW_NUMBER() như LAST_ENTRYDATE, cùng sub-select N16.</t>
+        </is>
+      </c>
+      <c r="E52" s="31" t="inlineStr">
+        <is>
+          <t>N16.REMARKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="28" t="inlineStr">
         <is>
           <t>PROPOSED_AMT</t>
         </is>
       </c>
-      <c r="B46" s="25" t="inlineStr">
+      <c r="B53" s="25" t="inlineStr">
         <is>
           <t>NUMBER(20,2)</t>
         </is>
       </c>
-      <c r="C46" s="26" t="inlineStr">
+      <c r="C53" s="26" t="inlineStr">
         <is>
           <t>Số tiền đề xuất</t>
         </is>
       </c>
-      <c r="D46" s="54" t="inlineStr">
+      <c r="D53" s="54" t="inlineStr">
         <is>
           <t>Số tiền đề xuất</t>
         </is>
       </c>
-      <c r="E46" s="31" t="inlineStr">
+      <c r="E53" s="31" t="inlineStr">
         <is>
           <t>A.PROPOSED_AMT</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="28" t="inlineStr">
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="28" t="inlineStr">
         <is>
           <t>CREDIT_LIMIT_APPROVAL</t>
         </is>
       </c>
-      <c r="B47" s="25" t="inlineStr">
+      <c r="B54" s="25" t="inlineStr">
         <is>
           <t>NUMBER(20,2)</t>
         </is>
       </c>
-      <c r="C47" s="26" t="inlineStr">
+      <c r="C54" s="26" t="inlineStr">
         <is>
           <t>Hạn mức chuyên gia phê duyệt</t>
         </is>
       </c>
-      <c r="D47" s="54" t="inlineStr">
+      <c r="D54" s="54" t="inlineStr">
         <is>
           <t>Hạn mức do chuyên gia phê duyệt</t>
         </is>
       </c>
-      <c r="E47" s="31" t="inlineStr">
+      <c r="E54" s="31" t="inlineStr">
         <is>
           <t>A.CREDIT_LIMIT_APPROVAL</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="28" t="inlineStr">
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="28" t="inlineStr">
         <is>
           <t>APPROVED_AMT_FINAL</t>
         </is>
       </c>
-      <c r="B48" s="25" t="inlineStr">
+      <c r="B55" s="25" t="inlineStr">
         <is>
           <t>NUMBER(20,2)</t>
         </is>
       </c>
-      <c r="C48" s="26" t="inlineStr">
-        <is>
-          <t>Hạn mức phê duyệt cuối cùng</t>
-        </is>
-      </c>
-      <c r="D48" s="54" t="inlineStr">
+      <c r="C55" s="26" t="inlineStr">
+        <is>
+          <t>Hạn mức phê duyệt cuối</t>
+        </is>
+      </c>
+      <c r="D55" s="54" t="inlineStr">
         <is>
           <t>Hạn mức phê duyệt cuối cùng (BC1.LOAN_AMOUNT, BC3.CREDIT_LIMIT)</t>
         </is>
       </c>
-      <c r="E48" s="31" t="inlineStr">
+      <c r="E55" s="31" t="inlineStr">
         <is>
           <t>A.APPROVED_AMT_FINAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="28" t="inlineStr">
-        <is>
-          <t>APPROVED_TERM</t>
-        </is>
-      </c>
-      <c r="B49" s="25" t="inlineStr">
-        <is>
-          <t>NVARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C49" s="26" t="inlineStr">
-        <is>
-          <t>Kỳ hạn phê duyệt</t>
-        </is>
-      </c>
-      <c r="D49" s="54" t="inlineStr">
-        <is>
-          <t>Kỳ hạn phê duyệt, giữ nguyên văn gốc vì có giá trị không ép được sang số</t>
-        </is>
-      </c>
-      <c r="E49" s="31" t="inlineStr">
-        <is>
-          <t>A.APPROVED_TERM</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="28" t="inlineStr">
-        <is>
-          <t>INTEREST_RATE_PCT</t>
-        </is>
-      </c>
-      <c r="B50" s="25" t="inlineStr">
-        <is>
-          <t>NVARCHAR2(500)</t>
-        </is>
-      </c>
-      <c r="C50" s="26" t="inlineStr">
-        <is>
-          <t>Lãi suất phê duyệt</t>
-        </is>
-      </c>
-      <c r="D50" s="54" t="inlineStr">
-        <is>
-          <t>Lãi suất phê duyệt (%), giữ nguyên văn gốc vì có giá trị không ép được sang số</t>
-        </is>
-      </c>
-      <c r="E50" s="31" t="inlineStr">
-        <is>
-          <t>A.INTEREST_RATE_PCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="28" t="inlineStr">
-        <is>
-          <t>CURRENCY_CODE</t>
-        </is>
-      </c>
-      <c r="B51" s="25" t="inlineStr">
-        <is>
-          <t>NVARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C51" s="26" t="inlineStr">
-        <is>
-          <t>Loại tiền</t>
-        </is>
-      </c>
-      <c r="D51" s="54" t="inlineStr">
-        <is>
-          <t>Loại tiền</t>
-        </is>
-      </c>
-      <c r="E51" s="31" t="inlineStr">
-        <is>
-          <t>A.CURRENCY_CODE</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="28" t="inlineStr">
-        <is>
-          <t>APPLICATION_LINK_INFO</t>
-        </is>
-      </c>
-      <c r="B52" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(200)</t>
-        </is>
-      </c>
-      <c r="C52" s="26" t="inlineStr">
-        <is>
-          <t>Thông tin liên kết hồ sơ</t>
-        </is>
-      </c>
-      <c r="D52" s="54" t="inlineStr">
-        <is>
-          <t>Thông tin liên kết hồ sơ — cột generic của WFINSTRUMENTTABLE — đổi tên từ VAR_STR12</t>
-        </is>
-      </c>
-      <c r="E52" s="31" t="inlineStr">
-        <is>
-          <t>A.APPLICATION_LINK_INFO</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="45" customHeight="1">
-      <c r="A53" s="28" t="inlineStr">
-        <is>
-          <t>UNDERWRITERMAKER_USERMAKE</t>
-        </is>
-      </c>
-      <c r="B53" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C53" s="26" t="inlineStr">
-        <is>
-          <t>User làm bước UnderwriterMaker</t>
-        </is>
-      </c>
-      <c r="D53" s="54" t="inlineStr">
-        <is>
-          <t>PHÁI SINH, COALESCE ĐÃ TÍNH XONG TẠI SB_DWH</t>
-        </is>
-      </c>
-      <c r="E53" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT D.UNDERWRITERMAKER_USERMAKE FROM D WHERE D.WORKSTEP_CODE = 'UnderwriterMaker' AND D.WI_NAME = A.WI_NAME ORDER BY D.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="45" customHeight="1">
-      <c r="A54" s="28" t="inlineStr">
-        <is>
-          <t>UNDERWRITERCHECKER_USERMAKE</t>
-        </is>
-      </c>
-      <c r="B54" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C54" s="26" t="inlineStr">
-        <is>
-          <t>User làm bước UnderwriterChecker</t>
-        </is>
-      </c>
-      <c r="D54" s="54" t="inlineStr">
-        <is>
-          <t>PHÁI SINH, COALESCE ĐÃ TÍNH XONG TẠI SB_DWH</t>
-        </is>
-      </c>
-      <c r="E54" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT D.UNDERWRITERCHECKER_USERMAKE FROM D WHERE D.WORKSTEP_CODE = 'UnderwriterChecker' AND D.WI_NAME = A.WI_NAME ORDER BY D.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="45" customHeight="1">
-      <c r="A55" s="28" t="inlineStr">
-        <is>
-          <t>APPROVAL_USERMAKE</t>
-        </is>
-      </c>
-      <c r="B55" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C55" s="26" t="inlineStr">
-        <is>
-          <t>User làm bước phê duyệt</t>
-        </is>
-      </c>
-      <c r="D55" s="54" t="inlineStr">
-        <is>
-          <t>PHÁI SINH, COALESCE ĐÃ TÍNH XONG TẠI SB_DWH</t>
-        </is>
-      </c>
-      <c r="E55" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT D.APPROVAL_USERMAKE FROM D WHERE D.WORKSTEP_CODE IN ('CreditCommittee','CreditApproval') AND D.WI_NAME = A.WI_NAME ORDER BY D.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="28" t="inlineStr">
         <is>
-          <t>LG_REQ</t>
+          <t>APPROVED_TERM</t>
         </is>
       </c>
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(10)</t>
+          <t>NVARCHAR2(100)</t>
         </is>
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>Cờ yêu cầu bảo lãnh</t>
+          <t>Kỳ hạn phê duyệt</t>
         </is>
       </c>
       <c r="D56" s="54" t="inlineStr">
         <is>
-          <t>Cờ yêu cầu bảo lãnh (Letter of Guarantee) phát sinh theo hồ sơ</t>
+          <t>Kỳ hạn phê duyệt, giữ nguyên văn gốc vì có giá trị không ép được sang số</t>
         </is>
       </c>
       <c r="E56" s="31" t="inlineStr">
         <is>
-          <t>A.LG_REQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="15" customHeight="1">
+          <t>A.APPROVED_TERM</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
       <c r="A57" s="28" t="inlineStr">
         <is>
-          <t>FI_REQ</t>
+          <t>INTEREST_RATE_PCT</t>
         </is>
       </c>
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(10)</t>
+          <t>NVARCHAR2(500)</t>
         </is>
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>Cờ yêu cầu FI</t>
+          <t>Lãi suất phê duyệt</t>
         </is>
       </c>
       <c r="D57" s="54" t="inlineStr">
         <is>
-          <t>Cờ yêu cầu (tương tự LG_REQ)</t>
+          <t>Lãi suất phê duyệt (%), giữ nguyên văn gốc vì có giá trị không ép được sang số</t>
         </is>
       </c>
       <c r="E57" s="31" t="inlineStr">
         <is>
-          <t>A.FI_REQ</t>
+          <t>A.INTEREST_RATE_PCT</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="28" t="inlineStr">
         <is>
-          <t>PHONE_REQ</t>
+          <t>CURRENCY_CODE</t>
         </is>
       </c>
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(10)</t>
+          <t>NVARCHAR2(100)</t>
         </is>
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>Cờ yêu cầu xác minh điện thoại</t>
+          <t>Loại tiền</t>
         </is>
       </c>
       <c r="D58" s="54" t="inlineStr">
         <is>
-          <t>Cờ yêu cầu xác minh điện thoại (tương tự LG_REQ)</t>
+          <t>Loại tiền</t>
         </is>
       </c>
       <c r="E58" s="31" t="inlineStr">
         <is>
-          <t>A.PHONE_REQ</t>
+          <t>A.CURRENCY_CODE</t>
         </is>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="28" t="inlineStr">
         <is>
-          <t>LAST_WORKSTEP</t>
+          <t>APPLICATION_LINK_INFO</t>
         </is>
       </c>
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(50)</t>
+          <t>VARCHAR2(200)</t>
         </is>
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>Tên bước hoàn tất gần nhất</t>
+          <t>Thông tin liên kết hồ sơ</t>
         </is>
       </c>
       <c r="D59" s="54" t="inlineStr">
         <is>
-          <t>Tên bước hoàn tất gần nhất, chuẩn hóa dùng chung 2 hệ — PHÁI SINH TẠI PDTD_DTM</t>
+          <t>Thông tin liên kết hồ sơ — cột generic của WFINSTRUMENTTABLE — đổi tên từ VAR_STR12</t>
         </is>
       </c>
       <c r="E59" s="31" t="inlineStr">
         <is>
-          <t>LEFT JOIN F ON F.WORKSTEP_CODE = E2.WORKSTEP_CODE AND F.DECISION_CODE = E2.DECISION_CODE → F.WORKSTEP_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="60" customHeight="1">
+          <t>A.APPLICATION_LINK_INFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="75" customHeight="1">
       <c r="A60" s="28" t="inlineStr">
         <is>
-          <t>BUSINESS_FLOW</t>
+          <t>UNDERWRITERMAKER_USERMAKE</t>
         </is>
       </c>
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(50)</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>Luồng nghiệp vụ chuẩn hóa</t>
+          <t>User Maker CVTĐ</t>
         </is>
       </c>
       <c r="D60" s="54" t="inlineStr">
         <is>
-          <t>Luồng nghiệp vụ chuẩn hóa để hiển thị trên báo cáo — CHUYỂN TỪ DIM_CLOS_APPLICATION</t>
+          <t>PHÁI SINH, COALESCE ĐÃ TÍNH XONG TẠI SB_DWH. [CẦN REVIEW] LLD viết ORDER BY ENTRYDATE DESC FETCH FIRST 1 ROW ONLY không kèm PARTITION BY — rewrite sang ROW_NUMBER() OVER (PARTITION BY WI_NAME ORDER BY ENTRYDATE DESC) = 1 để giữ đúng 1 dòng/hồ sơ.</t>
         </is>
       </c>
       <c r="E60" s="31" t="inlineStr">
         <is>
-          <t>LEFT JOIN B ON B.DIMENSION_KEY = A.CUSTOMER_SK → CASE WHEN B.CUST_GROUP IN ('MSME','SME','USME') THEN 'PDTD_KHDN' WHEN B.CUST_GROUP IN ('NBFI','JSC','FDI','BANK','STR','SOC') THEN 'PDTD_KHDNL' ELSE NULL END</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="270" customHeight="1">
+          <t>N5.UNDERWRITERMAKER_USERMAKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="45" customHeight="1">
       <c r="A61" s="28" t="inlineStr">
         <is>
-          <t>REF_PRODUCT</t>
+          <t>UNDERWRITERCHECKER_USERMAKE</t>
         </is>
       </c>
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(200)</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>Nhóm sản phẩm tra SLA</t>
+          <t>User Checker CVTĐ</t>
         </is>
       </c>
       <c r="D61" s="54" t="inlineStr">
         <is>
-          <t>Nhóm sản phẩm dùng để tra cam kết SLA (BC5) — CHUYỂN TỪ DIM_CLOS_APPLICATION</t>
+          <t>PHÁI SINH, COALESCE ĐÃ TÍNH XONG TẠI SB_DWH. [CẦN REVIEW] Cùng rewrite ROW_NUMBER() như UNDERWRITERMAKER_USERMAKE.</t>
         </is>
       </c>
       <c r="E61" s="31" t="inlineStr">
         <is>
-          <t>LEFT JOIN G ON G.PRODUCTLINE_SK = A.PRODUCTLINE_SK → LEFT JOIN H ON H.SUB_PRODUCT_SK = A.SUB_PRODUCT_SK → LEFT JOIN I ON I.DIMENSION_KEY = A.APPLICATION_SK → LEFT JOIN B ON B.DIMENSION_KEY = A.CUSTOMER_SK → LEFT JOIN J ON (CASE WHEN A.CHANGE_REQUEST = 'Change Request' THEN J.PRODUCT_LINE = 'Trường Change Request' ELSE J.PRODUCT_LINE = G.PRODUCTLINE_NAME END) AND (J.SUB_PRODUCT IS NULL OR J.SUB_PRODUCT = H.SUB_PRODUCT_NAME) AND J.HAVE_ANY_DEVIATION = I.HAVE_ANY_DEVIATION AND J.FLAG_APP_GRP = CASE WHEN I.APP_GRP IN ('A1','A2','B1','B2') THEN 'CGPD' WHEN I.APP_GRP IN ('BOD','CC','SCC','RCC') THEN 'HDTD' END AND B.CUST_GROUP IN ('NBFI','JSC','FDI','BANK','STR','SOC') → LEFT JOIN K ON (CASE WHEN A.CHANGE_REQUEST = 'Change Request' THEN K.PRODUCT_LINE = 'Trường Change Request' ELSE K.PRODUCT_LINE = G.PRODUCTLINE_NAME END) AND (K.SUB_PRODUCT IS NULL OR K.SUB_PRODUCT = H.SUB_PRODUCT_NAME) AND K.HAVE_ANY_DEVIATION = I.HAVE_ANY_DEVIATION AND K.FLAG_APP_GRP = CASE WHEN I.APP_GRP IN ('A1','A2','B1','B2') THEN 'CGPD' WHEN I.APP_GRP IN ('BOD','CC','SCC','RCC') THEN 'HDTD' END AND B.CUST_GROUP IN ('MSME','SME','USME','C1') → COALESCE(J.REF_PRODUCT, K.REF_PRODUCT)</t>
+          <t>N6.UNDERWRITERCHECKER_USERMAKE</t>
         </is>
       </c>
     </row>
     <row r="62" ht="60" customHeight="1">
       <c r="A62" s="28" t="inlineStr">
         <is>
+          <t>APPROVAL_USERMAKE</t>
+        </is>
+      </c>
+      <c r="B62" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C62" s="26" t="inlineStr">
+        <is>
+          <t>User Maker phê duyệt</t>
+        </is>
+      </c>
+      <c r="D62" s="54" t="inlineStr">
+        <is>
+          <t>PHÁI SINH, COALESCE ĐÃ TÍNH XONG TẠI SB_DWH. [CẦN REVIEW] Cùng rewrite ROW_NUMBER() như UNDERWRITERMAKER_USERMAKE, nhóm theo WORKSTEP_CODE IN ('CreditCommittee','CreditApproval').</t>
+        </is>
+      </c>
+      <c r="E62" s="31" t="inlineStr">
+        <is>
+          <t>N17.APPROVAL_USERMAKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="28" t="inlineStr">
+        <is>
+          <t>LG_REQ</t>
+        </is>
+      </c>
+      <c r="B63" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(10)</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="inlineStr">
+        <is>
+          <t>Cờ yêu cầu bảo lãnh</t>
+        </is>
+      </c>
+      <c r="D63" s="54" t="inlineStr">
+        <is>
+          <t>Cờ yêu cầu bảo lãnh (Letter of Guarantee) phát sinh theo hồ sơ</t>
+        </is>
+      </c>
+      <c r="E63" s="31" t="inlineStr">
+        <is>
+          <t>A.LG_REQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="28" t="inlineStr">
+        <is>
+          <t>FI_REQ</t>
+        </is>
+      </c>
+      <c r="B64" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(10)</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="inlineStr">
+        <is>
+          <t>Cờ yêu cầu FI</t>
+        </is>
+      </c>
+      <c r="D64" s="54" t="inlineStr">
+        <is>
+          <t>Cờ yêu cầu (tương tự LG_REQ)</t>
+        </is>
+      </c>
+      <c r="E64" s="31" t="inlineStr">
+        <is>
+          <t>A.FI_REQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="28" t="inlineStr">
+        <is>
+          <t>PHONE_REQ</t>
+        </is>
+      </c>
+      <c r="B65" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(10)</t>
+        </is>
+      </c>
+      <c r="C65" s="26" t="inlineStr">
+        <is>
+          <t>Cờ yêu cầu xác minh điện thoại</t>
+        </is>
+      </c>
+      <c r="D65" s="54" t="inlineStr">
+        <is>
+          <t>Cờ yêu cầu xác minh điện thoại (tương tự LG_REQ)</t>
+        </is>
+      </c>
+      <c r="E65" s="31" t="inlineStr">
+        <is>
+          <t>A.PHONE_REQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="135" customHeight="1">
+      <c r="A66" s="28" t="inlineStr">
+        <is>
+          <t>LAST_WORKSTEP</t>
+        </is>
+      </c>
+      <c r="B66" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(50)</t>
+        </is>
+      </c>
+      <c r="C66" s="26" t="inlineStr">
+        <is>
+          <t>Bước hồ sơ cuối</t>
+        </is>
+      </c>
+      <c r="D66" s="54" t="inlineStr">
+        <is>
+          <t>Tên bước hoàn tất gần nhất, chuẩn hóa dùng chung 2 hệ — PHÁI SINH TẠI PDTD_DTM. [CẦN REVIEW] note của LLD đề cập hop qua WORKSTEP_DECISION_SK (cột cùng bảng, đã bê 1:1 từ STG_FCT_CLOS_APPLICATION) → STG_DIM_CLOS_WORKSTEP_DECISION, nhưng etl_logic chỉ viết sẵn đúng 1 JOIN tới E theo WORKSTEP_CODE/DECISION_CODE của F — JOIN chuỗi A→F có thể chưa được viết đầy đủ, cần xác nhận lại chuỗi 2 hop (A.WORKSTEP_DECISION_SK → F.DIMENSION_KEY → F.WORKSTEP_CODE/DECISION_CODE → E).</t>
+        </is>
+      </c>
+      <c r="E66" s="31" t="inlineStr">
+        <is>
+          <t>E.WORKSTEP_NAME_STD</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="45" customHeight="1">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>BUSINESS_FLOW</t>
+        </is>
+      </c>
+      <c r="B67" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(50)</t>
+        </is>
+      </c>
+      <c r="C67" s="26" t="inlineStr">
+        <is>
+          <t>Phân khúc hồ sơ</t>
+        </is>
+      </c>
+      <c r="D67" s="54" t="inlineStr">
+        <is>
+          <t>Luồng nghiệp vụ chuẩn hóa để hiển thị trên báo cáo — CHUYỂN TỪ DIM_CLOS_APPLICATION</t>
+        </is>
+      </c>
+      <c r="E67" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN B.CUST_GROUP IN ('MSME','SME','USME') THEN 'PDTD_KHDN' WHEN B.CUST_GROUP IN ('NBFI','JSC','FDI','BANK','STR','SOC') THEN 'PDTD_KHDNL' ELSE NULL END</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" s="28" t="inlineStr">
+        <is>
+          <t>REF_PRODUCT</t>
+        </is>
+      </c>
+      <c r="B68" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C68" s="26" t="inlineStr">
+        <is>
+          <t>Nhóm sản phẩm tra SLA</t>
+        </is>
+      </c>
+      <c r="D68" s="54" t="inlineStr">
+        <is>
+          <t>Nhóm sản phẩm dùng để tra cam kết SLA (BC5) — CHUYỂN TỪ DIM_CLOS_APPLICATION. Nhánh rẽ Product Line dựa trên CHANGE_REQUEST='Change Request'; APP_GRP='C1' xếp vào nhánh K.</t>
+        </is>
+      </c>
+      <c r="E68" s="31" t="inlineStr">
+        <is>
+          <t>COALESCE(J.REF_PRODUCT, K.REF_PRODUCT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="45" customHeight="1">
+      <c r="A69" s="28" t="inlineStr">
+        <is>
           <t>SLA_CREDIT_OFFICER</t>
         </is>
       </c>
-      <c r="B62" s="25" t="inlineStr">
+      <c r="B69" s="25" t="inlineStr">
         <is>
           <t>NUMBER(10,2)</t>
         </is>
       </c>
-      <c r="C62" s="26" t="inlineStr">
-        <is>
-          <t>Cam kết giờ chuyên viên tín dụng</t>
-        </is>
-      </c>
-      <c r="D62" s="54" t="inlineStr">
-        <is>
-          <t>Cam kết giờ cho chuyên viên tín dụng — CHUYỂN TỪ DIM_CLOS_APPLICATION. APP_GRP='C1' không nằm trong điều kiện CUST_GROUP của JOIN nào — cả 2 JOIN đều NULL, override bằng hằng số cứng 4 giờ</t>
-        </is>
-      </c>
-      <c r="E62" s="31" t="inlineStr">
+      <c r="C69" s="26" t="inlineStr">
+        <is>
+          <t>Cam kết SLA chuyên viên tín dụng</t>
+        </is>
+      </c>
+      <c r="D69" s="54" t="inlineStr">
+        <is>
+          <t>Cam kết giờ cho chuyên viên tín dụng — CHUYỂN TỪ DIM_CLOS_APPLICATION. APP_GRP='C1' dùng hằng số cứng 4 giờ, không lookup.</t>
+        </is>
+      </c>
+      <c r="E69" s="31" t="inlineStr">
         <is>
           <t>CASE WHEN I.APP_GRP = 'C1' THEN 4 ELSE COALESCE(J.SLA_CREDIT_OFFICER, K.SLA_CREDIT_OFFICER) END</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="45" customHeight="1">
-      <c r="A63" s="28" t="inlineStr">
-        <is>
-          <t>SLA_MARKER</t>
-        </is>
-      </c>
-      <c r="B63" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER(10,2)</t>
-        </is>
-      </c>
-      <c r="C63" s="26" t="inlineStr">
-        <is>
-          <t>Cam kết giờ lập hồ sơ thẩm định</t>
-        </is>
-      </c>
-      <c r="D63" s="54" t="inlineStr">
-        <is>
-          <t>Cam kết giờ cho bước lập hồ sơ thẩm định — CHUYỂN TỪ DIM_CLOS_APPLICATION, cùng JOIN với REF_PRODUCT (cột cùng bảng)</t>
-        </is>
-      </c>
-      <c r="E63" s="31" t="inlineStr">
-        <is>
-          <t>CASE WHEN I.APP_GRP = 'C1' THEN 4 ELSE COALESCE(J.SLA_MARKER, K.SLA_MARKER) END</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="45" customHeight="1">
-      <c r="A64" s="28" t="inlineStr">
-        <is>
-          <t>SLA_CHECKER</t>
-        </is>
-      </c>
-      <c r="B64" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER(10,2)</t>
-        </is>
-      </c>
-      <c r="C64" s="26" t="inlineStr">
-        <is>
-          <t>Cam kết giờ kiểm soát thẩm định</t>
-        </is>
-      </c>
-      <c r="D64" s="54" t="inlineStr">
-        <is>
-          <t>Cam kết giờ cho bước kiểm soát thẩm định — CHUYỂN TỪ DIM_CLOS_APPLICATION, cùng JOIN với REF_PRODUCT (cột cùng bảng)</t>
-        </is>
-      </c>
-      <c r="E64" s="31" t="inlineStr">
-        <is>
-          <t>CASE WHEN I.APP_GRP = 'C1' THEN 4 ELSE COALESCE(J.SLA_CHECKER, K.SLA_CHECKER) END</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="45" customHeight="1">
-      <c r="A65" s="28" t="inlineStr">
-        <is>
-          <t>SLA_CREDIT_APPROVER</t>
-        </is>
-      </c>
-      <c r="B65" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER(10,2)</t>
-        </is>
-      </c>
-      <c r="C65" s="26" t="inlineStr">
-        <is>
-          <t>Cam kết giờ cấp phê duyệt</t>
-        </is>
-      </c>
-      <c r="D65" s="54" t="inlineStr">
-        <is>
-          <t>Cam kết giờ cho cấp phê duyệt — CHUYỂN TỪ DIM_CLOS_APPLICATION, cùng JOIN với REF_PRODUCT (cột cùng bảng)</t>
-        </is>
-      </c>
-      <c r="E65" s="31" t="inlineStr">
-        <is>
-          <t>CASE WHEN I.APP_GRP = 'C1' THEN 4 ELSE COALESCE(J.SLA_CREDIT_APPROVER, K.SLA_CREDIT_APPROVER) END</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" s="28" t="inlineStr">
-        <is>
-          <t>LEGAL_REPRESENTATIVE</t>
-        </is>
-      </c>
-      <c r="B66" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(1000)</t>
-        </is>
-      </c>
-      <c r="C66" s="26" t="inlineStr">
-        <is>
-          <t>Người đại diện theo pháp luật</t>
-        </is>
-      </c>
-      <c r="D66" s="54" t="inlineStr">
-        <is>
-          <t>Người đại diện theo pháp luật (BC2) — CHUYỂN TỪ DIM_CLOS_CUSTOMER</t>
-        </is>
-      </c>
-      <c r="E66" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN I ON I.DIMENSION_KEY = A.APPLICATION_SK → LEFT JOIN (SELECT L2.WI_NAME, LISTAGG(L2.FULL_NAME, ';') AS LEGAL_REPRESENTATIVE FROM L L2 WHERE L2.OBJ_TYPE = 'Người đại diện theo pháp luật' GROUP BY L2.WI_NAME) LP ON LP.WI_NAME = I.WI_NAME → LP.LEGAL_REPRESENTATIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" s="28" t="inlineStr">
-        <is>
-          <t>ADD_ID_REPRESENTATIVE</t>
-        </is>
-      </c>
-      <c r="B67" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(1000)</t>
-        </is>
-      </c>
-      <c r="C67" s="26" t="inlineStr">
-        <is>
-          <t>Số giấy tờ người đại diện pháp luật</t>
-        </is>
-      </c>
-      <c r="D67" s="54" t="inlineStr">
-        <is>
-          <t>Số giấy tờ tùy thân của người đại diện theo pháp luật (BC2) — CHUYỂN TỪ DIM_CLOS_CUSTOMER. KHÔNG ETL ORG_LEGAL_ID — báo cáo tự JOIN report-time khi cần</t>
-        </is>
-      </c>
-      <c r="E67" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN I ON I.DIMENSION_KEY = A.APPLICATION_SK → LEFT JOIN (SELECT L2.WI_NAME, LISTAGG(L2.ID_NUMBER, ';') AS ADD_ID_REPRESENTATIVE FROM L L2 WHERE L2.OBJ_TYPE = 'Người đại diện theo pháp luật' GROUP BY L2.WI_NAME) LP ON LP.WI_NAME = I.WI_NAME → LP.ADD_ID_REPRESENTATIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="75" customHeight="1">
-      <c r="A68" s="28" t="inlineStr">
-        <is>
-          <t>APPLICATION_STATUS</t>
-        </is>
-      </c>
-      <c r="B68" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(50)</t>
-        </is>
-      </c>
-      <c r="C68" s="26" t="inlineStr">
-        <is>
-          <t>Trạng thái hồ sơ chuẩn hóa</t>
-        </is>
-      </c>
-      <c r="D68" s="54" t="inlineStr">
-        <is>
-          <t>Trạng thái hồ sơ chuẩn hóa (BC2) — PHÁI SINH TẠI PDTD_DTM, CHUYỂN TỪ SB_DWH (đồng bộ theo pattern RLOS)</t>
-        </is>
-      </c>
-      <c r="E68" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN E2 ON E2.DIMENSION_KEY = A.WORKSTEP_DECISION_SK → CASE WHEN E2.DECISION_CODE IN ('Submit','Send To PostSanction','Submit To DisbursementMaker','Send To HOSupport') THEN 'Approved' WHEN E2.DECISION_CODE = 'Reject' THEN 'Rejected' WHEN E2.WORKSTEP_CODE IN ('CancelRevoke','CancelPermanent') THEN 'Cancelled' ELSE 'Processing' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" s="28" t="inlineStr">
-        <is>
-          <t>FLAG_AUTO_CANCEL</t>
-        </is>
-      </c>
-      <c r="B69" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(10)</t>
-        </is>
-      </c>
-      <c r="C69" s="26" t="inlineStr">
-        <is>
-          <t>Cờ tự động hủy</t>
-        </is>
-      </c>
-      <c r="D69" s="54" t="inlineStr">
-        <is>
-          <t>'YES'/'NO' theo nguyên văn SRS BC2 field FLAG_AUTO_CAN — PHÁI SINH TẠI PDTD_DTM, CHUYỂN TỪ SB_DWH. CANCEL_DATE là cột phái sinh TẠI CHÍNH BẢNG này (cùng bảng), không tồn tại trên STG_FCT_CLOS_APPLICATION</t>
-        </is>
-      </c>
-      <c r="E69" s="31" t="inlineStr">
-        <is>
-          <t>CASE WHEN A.CANCEL_DATE IS NOT NULL AND (SELECT E2.DECISION_CODE FROM E2 WHERE E2.DIMENSION_KEY = A.WORKSTEP_DECISION_SK) = 'Auto-Cancel' THEN 'YES' ELSE 'NO' END</t>
         </is>
       </c>
     </row>
     <row r="70" ht="45" customHeight="1">
       <c r="A70" s="28" t="inlineStr">
         <is>
-          <t>APPROVAL_TYPE</t>
+          <t>SLA_MARKER</t>
         </is>
       </c>
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(200)</t>
+          <t>NUMBER(10,2)</t>
         </is>
       </c>
       <c r="C70" s="26" t="inlineStr">
         <is>
-          <t>Loại luồng phê duyệt</t>
+          <t>Cam kết SLA lập hồ sơ thẩm định</t>
         </is>
       </c>
       <c r="D70" s="54" t="inlineStr">
         <is>
-          <t>Loại luồng phê duyệt (BC2) — PHÁI SINH TẠI PDTD_DTM. Điều kiện lọc dùng UPPER() ở cả 2 phía — chưa xác nhận case thật trên STREAM nguồn</t>
+          <t>Cam kết giờ cho bước lập hồ sơ thẩm định — CHUYỂN TỪ DIM_CLOS_APPLICATION. APP_GRP='C1' dùng hằng số cứng 4 giờ, không lookup.</t>
         </is>
       </c>
       <c r="E70" s="31" t="inlineStr">
         <is>
-          <t>LEFT JOIN I ON I.DIMENSION_KEY = A.APPLICATION_SK → CASE WHEN UPPER(I.STREAM) IN (UPPER('Phê duyệt tín dụng'), UPPER('Sent To Disbursement Request')) THEN I.STREAM ELSE NULL END</t>
+          <t>CASE WHEN I.APP_GRP = 'C1' THEN 4 ELSE COALESCE(J.SLA_MARKER, K.SLA_MARKER) END</t>
         </is>
       </c>
     </row>
     <row r="71" ht="45" customHeight="1">
       <c r="A71" s="28" t="inlineStr">
         <is>
-          <t>CHANGE_REQUEST</t>
+          <t>SLA_CHECKER</t>
         </is>
       </c>
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(200)</t>
+          <t>NUMBER(10,2)</t>
         </is>
       </c>
       <c r="C71" s="26" t="inlineStr">
         <is>
-          <t>Yêu cầu điều chỉnh hồ sơ</t>
+          <t>Cam kết SLA kiểm soát thẩm định</t>
         </is>
       </c>
       <c r="D71" s="54" t="inlineStr">
         <is>
-          <t>Yêu cầu điều chỉnh hồ sơ — bê 1:1 từ SB_DWH.FCT_CLOS_APPLICATION.CHANGE_REQUEST (nguồn gốc xa: NG_SB_CLOS_CHANGEREQ.CHANGE_REQUEST)</t>
+          <t>Cam kết giờ cho bước kiểm soát thẩm định — CHUYỂN TỪ DIM_CLOS_APPLICATION. APP_GRP='C1' dùng hằng số cứng 4 giờ, không lookup.</t>
         </is>
       </c>
       <c r="E71" s="31" t="inlineStr">
         <is>
-          <t>A.CHANGE_REQUEST</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="60" customHeight="1">
+          <t>CASE WHEN I.APP_GRP = 'C1' THEN 4 ELSE COALESCE(J.SLA_CHECKER, K.SLA_CHECKER) END</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="45" customHeight="1">
       <c r="A72" s="28" t="inlineStr">
         <is>
-          <t>CHANGE_TYPE</t>
+          <t>SLA_CREDIT_APPROVER</t>
         </is>
       </c>
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(500)</t>
+          <t>NUMBER(10,2)</t>
         </is>
       </c>
       <c r="C72" s="26" t="inlineStr">
         <is>
-          <t>Loại thay đổi điều kiện phê duyệt</t>
+          <t>Cam kết SLA cấp phê duyệt</t>
         </is>
       </c>
       <c r="D72" s="54" t="inlineStr">
         <is>
-          <t>Loại thay đổi điều kiện phê duyệt, giữ nguyên chuỗi gốc đa giá trị nối bằng dấu '~' — bê 1:1 từ SB_DWH.FCT_CLOS_APPLICATION.CHANGE_TYPE (nguồn gốc xa: NG_SB_CLOS_CHANGEREQ.CHANGE_TYPE)</t>
+          <t>Cam kết giờ cho cấp phê duyệt — CHUYỂN TỪ DIM_CLOS_APPLICATION. APP_GRP='C1' dùng hằng số cứng 4 giờ, không lookup.</t>
         </is>
       </c>
       <c r="E72" s="31" t="inlineStr">
         <is>
-          <t>A.CHANGE_TYPE</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="105" customHeight="1">
+          <t>CASE WHEN I.APP_GRP = 'C1' THEN 4 ELSE COALESCE(J.SLA_CREDIT_APPROVER, K.SLA_CREDIT_APPROVER) END</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="45" customHeight="1">
       <c r="A73" s="28" t="inlineStr">
         <is>
-          <t>HAS_DDE_FLAG</t>
+          <t>LEGAL_REPRESENTATIVE</t>
         </is>
       </c>
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(1)</t>
+          <t>VARCHAR2(1000)</t>
         </is>
       </c>
       <c r="C73" s="26" t="inlineStr">
         <is>
-          <t>Cờ đã tới DetailDataEntry</t>
+          <t>Người đại diện pháp luật</t>
         </is>
       </c>
       <c r="D73" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước DetailDataEntry', chỉ chuyển Y, không bao giờ quay lại N. Nguồn cho VOLUME (AGG_LOS_KPI_APPLICATION) thay cho EXISTS quét lịch sử WORKSTEP_EVENT. Carry-forward từ FCT_CLOS_APPLICATION_PREV (snapshot DAYID=v_batch_date-1, TRUNCATE+INSERT trước khi chạy batch) OR event mới trong batch hiện tại</t>
+          <t>Người đại diện theo pháp luật (BC2) — CHUYỂN TỪ DIM_CLOS_CUSTOMER. Nối chuỗi FULL_NAME bằng ';' nếu nhiều đại diện.</t>
         </is>
       </c>
       <c r="E73" s="31" t="inlineStr">
         <is>
-          <t>LEFT JOIN M ON M.WI_NAME = A.WI_NAME → CASE WHEN COALESCE(M.HAS_DDE_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM D WHERE D.WI_NAME = A.WI_NAME AND D.WORKSTEP_CODE = 'DetailDataEntry') THEN 'Y' ELSE 'N' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="75" customHeight="1">
+          <t>LP.LEGAL_REPRESENTATIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="60" customHeight="1">
       <c r="A74" s="28" t="inlineStr">
         <is>
-          <t>HAS_UWM_FLAG</t>
+          <t>ADD_ID_REPRESENTATIVE</t>
         </is>
       </c>
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(1)</t>
+          <t>VARCHAR2(1000)</t>
         </is>
       </c>
       <c r="C74" s="26" t="inlineStr">
         <is>
-          <t>Cờ đã tới UnderwriterMaker</t>
+          <t>Số giấy tờ người đại diện</t>
         </is>
       </c>
       <c r="D74" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước UnderwriterMaker'. Dùng cho carry-forward hồ sơ treo trên FCT_CLOS_WORKSTEP_EVENT (lọc phạm vi BC4) và nguồn cho VOLUME (AGG_LOS_KPI_APPLICATION). Cùng cơ chế carry-forward với HAS_DDE_FLAG</t>
+          <t>Số giấy tờ tùy thân của người đại diện theo pháp luật (BC2) — CHUYỂN TỪ DIM_CLOS_CUSTOMER. Cùng đường JOIN với LEGAL_REPRESENTATIVE, nối chuỗi ID_NUMBER bằng ';' nếu nhiều đại diện.</t>
         </is>
       </c>
       <c r="E74" s="31" t="inlineStr">
         <is>
-          <t>LEFT JOIN M ON M.WI_NAME = A.WI_NAME → CASE WHEN COALESCE(M.HAS_UWM_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM D WHERE D.WI_NAME = A.WI_NAME AND D.WORKSTEP_CODE = 'UnderwriterMaker') THEN 'Y' ELSE 'N' END</t>
+          <t>LP.ADD_ID_REPRESENTATIVE</t>
         </is>
       </c>
     </row>
     <row r="75" ht="60" customHeight="1">
       <c r="A75" s="28" t="inlineStr">
         <is>
+          <t>APPLICATION_STATUS</t>
+        </is>
+      </c>
+      <c r="B75" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(50)</t>
+        </is>
+      </c>
+      <c r="C75" s="26" t="inlineStr">
+        <is>
+          <t>Trạng thái cuối của hồ sơ</t>
+        </is>
+      </c>
+      <c r="D75" s="54" t="inlineStr">
+        <is>
+          <t>Trạng thái hồ sơ chuẩn hóa (BC2) — PHÁI SINH TẠI PDTD_DTM, CHUYỂN TỪ SB_DWH (đồng bộ theo pattern RLOS)</t>
+        </is>
+      </c>
+      <c r="E75" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN F.DECISION_CODE IN ('Submit','Send To PostSanction','Submit To DisbursementMaker','Send To HOSupport') THEN 'Approved' WHEN F.DECISION_CODE = 'Reject' THEN 'Rejected' WHEN F.WORKSTEP_CODE IN ('CancelRevoke','CancelPermanent') THEN 'Cancelled' ELSE 'Processing' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="45" customHeight="1">
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t>FLAG_AUTO_CANCEL</t>
+        </is>
+      </c>
+      <c r="B76" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(10)</t>
+        </is>
+      </c>
+      <c r="C76" s="26" t="inlineStr">
+        <is>
+          <t>Hồ sơ bị tự động hủy</t>
+        </is>
+      </c>
+      <c r="D76" s="54" t="inlineStr">
+        <is>
+          <t>'YES'/'NO' theo nguyên văn SRS BC2 field FLAG_AUTO_CAN (BC2) — PHÁI SINH TẠI PDTD_DTM, CHUYỂN TỪ SB_DWH</t>
+        </is>
+      </c>
+      <c r="E76" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN A.CANCEL_DATE IS NOT NULL AND (SELECT F.DECISION_CODE FROM F WHERE F.DIMENSION_KEY = A.WORKSTEP_DECISION_SK) = 'Auto-Cancel' THEN 'YES' ELSE 'NO' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="45" customHeight="1">
+      <c r="A77" s="28" t="inlineStr">
+        <is>
+          <t>APPROVAL_TYPE</t>
+        </is>
+      </c>
+      <c r="B77" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C77" s="26" t="inlineStr">
+        <is>
+          <t>Loại luồng phê duyệt</t>
+        </is>
+      </c>
+      <c r="D77" s="54" t="inlineStr">
+        <is>
+          <t>Loại luồng phê duyệt (BC2) — PHÁI SINH TẠI PDTD_DTM: STREAM tra qua APPLICATION_SK → I.STREAM (giữ nguyên giá trị gốc trên DIM, không ép case khi gán).</t>
+        </is>
+      </c>
+      <c r="E77" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN UPPER(I.STREAM) IN (UPPER('Phê duyệt tín dụng'), UPPER('Sent To Disbursement Request')) THEN I.STREAM ELSE NULL END</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="45" customHeight="1">
+      <c r="A78" s="28" t="inlineStr">
+        <is>
+          <t>CHANGE_REQUEST</t>
+        </is>
+      </c>
+      <c r="B78" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C78" s="26" t="inlineStr">
+        <is>
+          <t>Yêu cầu điều chỉnh hồ sơ</t>
+        </is>
+      </c>
+      <c r="D78" s="54" t="inlineStr">
+        <is>
+          <t>Yêu cầu điều chỉnh hồ sơ — bê 1:1 từ SB_DWH.FCT_CLOS_APPLICATION.CHANGE_REQUEST (nguồn gốc xa: NG_SB_CLOS_CHANGEREQ.CHANGE_REQUEST)</t>
+        </is>
+      </c>
+      <c r="E78" s="31" t="inlineStr">
+        <is>
+          <t>A.CHANGE_REQUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="45" customHeight="1">
+      <c r="A79" s="28" t="inlineStr">
+        <is>
+          <t>CHANGE_TYPE</t>
+        </is>
+      </c>
+      <c r="B79" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(500)</t>
+        </is>
+      </c>
+      <c r="C79" s="26" t="inlineStr">
+        <is>
+          <t>Loại thay đổi điều kiện</t>
+        </is>
+      </c>
+      <c r="D79" s="54" t="inlineStr">
+        <is>
+          <t>Loại thay đổi điều kiện phê duyệt, giữ nguyên chuỗi gốc đa giá trị nối bằng dấu '~' — bê 1:1 từ SB_DWH.FCT_CLOS_APPLICATION.CHANGE_TYPE</t>
+        </is>
+      </c>
+      <c r="E79" s="31" t="inlineStr">
+        <is>
+          <t>A.CHANGE_TYPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" s="28" t="inlineStr">
+        <is>
+          <t>HAS_DDE_FLAG</t>
+        </is>
+      </c>
+      <c r="B80" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(1)</t>
+        </is>
+      </c>
+      <c r="C80" s="26" t="inlineStr">
+        <is>
+          <t>Cờ đã tới DetailDataEntry</t>
+        </is>
+      </c>
+      <c r="D80" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước DetailDataEntry', chỉ chuyển Y, không bao giờ quay lại N. Nguồn cho VOLUME (AGG_LOS_KPI_APPLICATION) thay cho EXISTS quét lịch sử WORKSTEP_EVENT</t>
+        </is>
+      </c>
+      <c r="E80" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN COALESCE(M.HAS_DDE_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM STG_FCT_CLOS_WORKSTEP_EVENT e WHERE e.WI_NAME = A.WI_NAME AND e.WORKSTEP_CODE = 'DetailDataEntry') THEN 'Y' ELSE 'N' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" s="28" t="inlineStr">
+        <is>
+          <t>HAS_UWM_FLAG</t>
+        </is>
+      </c>
+      <c r="B81" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(1)</t>
+        </is>
+      </c>
+      <c r="C81" s="26" t="inlineStr">
+        <is>
+          <t>Cờ đã tới UnderwriterMaker</t>
+        </is>
+      </c>
+      <c r="D81" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước UnderwriterMaker'. Dùng cho carry-forward hồ sơ treo trên FCT_CLOS_WORKSTEP_EVENT (lọc phạm vi BC4) và nguồn cho VOLUME</t>
+        </is>
+      </c>
+      <c r="E81" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN COALESCE(M.HAS_UWM_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM STG_FCT_CLOS_WORKSTEP_EVENT e WHERE e.WI_NAME = A.WI_NAME AND e.WORKSTEP_CODE = 'UnderwriterMaker') THEN 'Y' ELSE 'N' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="45" customHeight="1">
+      <c r="A82" s="28" t="inlineStr">
+        <is>
           <t>HAS_UWC_FLAG</t>
         </is>
       </c>
-      <c r="B75" s="25" t="inlineStr">
+      <c r="B82" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(1)</t>
         </is>
       </c>
-      <c r="C75" s="26" t="inlineStr">
+      <c r="C82" s="26" t="inlineStr">
         <is>
           <t>Cờ đã tới UnderwriterChecker</t>
         </is>
       </c>
-      <c r="D75" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước UnderwriterChecker'. Nguồn cho VOLUME (AGG_LOS_KPI_APPLICATION, mức 0.6). Cùng cơ chế carry-forward với HAS_DDE_FLAG</t>
-        </is>
-      </c>
-      <c r="E75" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN M ON M.WI_NAME = A.WI_NAME → CASE WHEN COALESCE(M.HAS_UWC_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM D WHERE D.WI_NAME = A.WI_NAME AND D.WORKSTEP_CODE = 'UnderwriterChecker') THEN 'Y' ELSE 'N' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" s="28" t="inlineStr">
+      <c r="D82" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước UnderwriterChecker'. Nguồn cho VOLUME (mức 0.6)</t>
+        </is>
+      </c>
+      <c r="E82" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN COALESCE(M.HAS_UWC_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM STG_FCT_CLOS_WORKSTEP_EVENT e WHERE e.WI_NAME = A.WI_NAME AND e.WORKSTEP_CODE = 'UnderwriterChecker') THEN 'Y' ELSE 'N' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="45" customHeight="1">
+      <c r="A83" s="28" t="inlineStr">
         <is>
           <t>HAS_APPROVAL_FLAG</t>
         </is>
       </c>
-      <c r="B76" s="25" t="inlineStr">
+      <c r="B83" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(1)</t>
         </is>
       </c>
-      <c r="C76" s="26" t="inlineStr">
-        <is>
-          <t>Cờ đã tới bước phê duyệt</t>
-        </is>
-      </c>
-      <c r="D76" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước CreditApproval/CreditCommittee' (chưa cần đã có quyết định). Nguồn cho VOLUME (AGG_LOS_KPI_APPLICATION, mức 0.8). Cùng cơ chế carry-forward với HAS_DDE_FLAG</t>
-        </is>
-      </c>
-      <c r="E76" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN M ON M.WI_NAME = A.WI_NAME → CASE WHEN COALESCE(M.HAS_APPROVAL_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM D WHERE D.WI_NAME = A.WI_NAME AND D.WORKSTEP_CODE IN ('CreditApproval','CreditCommittee')) THEN 'Y' ELSE 'N' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="105" customHeight="1">
-      <c r="A77" s="28" t="inlineStr">
+      <c r="C83" s="26" t="inlineStr">
+        <is>
+          <t>Cờ đã tới cấp phê duyệt</t>
+        </is>
+      </c>
+      <c r="D83" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước CreditApproval/CreditCommittee' (chưa cần đã có quyết định). Nguồn cho VOLUME (mức 0.8)</t>
+        </is>
+      </c>
+      <c r="E83" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN COALESCE(M.HAS_APPROVAL_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM STG_FCT_CLOS_WORKSTEP_EVENT e WHERE e.WI_NAME = A.WI_NAME AND e.WORKSTEP_CODE IN ('CreditApproval','CreditCommittee')) THEN 'Y' ELSE 'N' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="90" customHeight="1">
+      <c r="A84" s="28" t="inlineStr">
         <is>
           <t>HAS_FINAL_APPROVAL_FLAG</t>
         </is>
       </c>
-      <c r="B77" s="25" t="inlineStr">
+      <c r="B84" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(1)</t>
         </is>
       </c>
-      <c r="C77" s="26" t="inlineStr">
-        <is>
-          <t>Cờ đã có quyết định phê duyệt hoàn tất</t>
-        </is>
-      </c>
-      <c r="D77" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã có quyết định phê duyệt hoàn tất' (case 1 của PROCESSED_DATE). Nguồn cho VOLUME mức 1.0 và điều kiện loại khỏi carry-forward hồ sơ treo. Cùng cơ chế carry-forward với HAS_DDE_FLAG, nhưng EXISTS cần JOIN thêm STG_DIM_CLOS_WORKSTEP_DECISION để lấy DECISION_CODE</t>
-        </is>
-      </c>
-      <c r="E77" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN M ON M.WI_NAME = A.WI_NAME → CASE WHEN COALESCE(M.HAS_FINAL_APPROVAL_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM D JOIN E2 ON E2.DIMENSION_KEY = D.WORKSTEP_DECISION_SK WHERE D.WI_NAME = A.WI_NAME AND D.WORKSTEP_CODE IN ('CreditApproval','CreditCommittee') AND E2.DECISION_CODE IN ('Submit','Send To PostSanction','Submit To DisbursementMaker','Send To HOSupport','Reject')) THEN 'Y' ELSE 'N' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" s="28" t="inlineStr">
+      <c r="C84" s="26" t="inlineStr">
+        <is>
+          <t>Cờ đã có quyết định phê duyệt</t>
+        </is>
+      </c>
+      <c r="D84" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã có quyết định phê duyệt hoàn tất' (case 1 của PROCESSED_DATE). Nguồn cho VOLUME (mức 1.0)</t>
+        </is>
+      </c>
+      <c r="E84" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN COALESCE(M.HAS_FINAL_APPROVAL_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM STG_FCT_CLOS_WORKSTEP_EVENT e JOIN F wd ON wd.DIMENSION_KEY = e.WORKSTEP_DECISION_SK WHERE e.WI_NAME = A.WI_NAME AND e.WORKSTEP_CODE IN ('CreditApproval','CreditCommittee') AND wd.DECISION_CODE IN ('Submit','Send To PostSanction','Submit To DisbursementMaker','Send To HOSupport','Reject')) THEN 'Y' ELSE 'N' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" s="28" t="inlineStr">
         <is>
           <t>HAS_CANCELLED_FLAG</t>
         </is>
       </c>
-      <c r="B78" s="25" t="inlineStr">
+      <c r="B85" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(1)</t>
         </is>
       </c>
-      <c r="C78" s="26" t="inlineStr">
-        <is>
-          <t>Cờ đã hủy hồ sơ</t>
-        </is>
-      </c>
-      <c r="D78" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã rơi vào CancelRevoke/CancelPermanent'. VOLUME dùng cờ này để xác nhận hồ sơ đã KẾT THÚC do hủy — khi đó lấy điểm theo bước xa nhất đã đạt thay vì NULL. Cùng cơ chế carry-forward với HAS_DDE_FLAG</t>
-        </is>
-      </c>
-      <c r="E78" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN M ON M.WI_NAME = A.WI_NAME → CASE WHEN COALESCE(M.HAS_CANCELLED_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM D WHERE D.WI_NAME = A.WI_NAME AND D.WORKSTEP_CODE IN ('CancelRevoke','CancelPermanent')) THEN 'Y' ELSE 'N' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="15" customHeight="1">
-      <c r="A81" s="55" t="inlineStr">
-        <is>
-          <t>Chú ý:</t>
-        </is>
-      </c>
-      <c r="B81" s="55" t="inlineStr">
-        <is>
-          <t>1. FCT_CLOS_APPLICATION_PREV (alias M) là snapshot DAYID=v_batch_date-1 của chính bảng FCT_CLOS_APPLICATION — phải TRUNCATE+INSERT bảng _PREV này TRƯỚC khi chạy batch ghi FCT_CLOS_APPLICATION, để tránh vừa đọc vừa ghi trên cùng bảng đích.</t>
+      <c r="C85" s="26" t="inlineStr">
+        <is>
+          <t>Cờ đã bị hủy</t>
+        </is>
+      </c>
+      <c r="D85" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã rơi vào CancelRevoke/CancelPermanent'. VOLUME dùng cờ này để xác nhận hồ sơ đã KẾT THÚC do hủy, lấy điểm theo bước xa nhất đã đạt trước khi hủy thay vì NULL</t>
+        </is>
+      </c>
+      <c r="E85" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN COALESCE(M.HAS_CANCELLED_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM STG_FCT_CLOS_WORKSTEP_EVENT e WHERE e.WI_NAME = A.WI_NAME AND e.WORKSTEP_CODE IN ('CancelRevoke','CancelPermanent')) THEN 'Y' ELSE 'N' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="10" t="n"/>
+      <c r="B87" s="10" t="n"/>
+      <c r="C87" s="10" t="n"/>
+      <c r="D87" s="55" t="inlineStr">
+        <is>
+          <t>Điều kiện join giữa các bảng</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="n"/>
+    </row>
+    <row r="88" ht="15" customHeight="1">
+      <c r="A88" s="25" t="n"/>
+      <c r="B88" s="25" t="n"/>
+      <c r="C88" s="51" t="n"/>
+      <c r="D88" s="54" t="n"/>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN B.DIMENSION_KEY = A.CUSTOMER_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1">
+      <c r="A89" s="25" t="n"/>
+      <c r="B89" s="25" t="n"/>
+      <c r="C89" s="51" t="n"/>
+      <c r="D89" s="54" t="n"/>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN C.LEGAL_ID = B.CUSTOMER_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="45" customHeight="1">
+      <c r="A90" s="25" t="n"/>
+      <c r="B90" s="25" t="n"/>
+      <c r="C90" s="51" t="n"/>
+      <c r="D90" s="54" t="n"/>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N1 (SELECT WI_NAME, USERNAME FROM STG_FCT_CLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE = 'RequestInitiate') N1 ON N1.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" s="25" t="n"/>
+      <c r="B91" s="25" t="n"/>
+      <c r="C91" s="51" t="n"/>
+      <c r="D91" s="54" t="n"/>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N2 (SELECT WI_NAME, USERNAME FROM STG_FCT_CLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE = 'BranchSupport' QUALIFY ROW_NUMBER() OVER (PARTITION BY WI_NAME ORDER BY EXITDATE DESC) = 1) N2 ON N2.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" s="25" t="n"/>
+      <c r="B92" s="25" t="n"/>
+      <c r="C92" s="51" t="n"/>
+      <c r="D92" s="54" t="n"/>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N3 (SELECT WI_NAME, USERNAME FROM STG_FCT_CLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE = 'DetailDataEntry' QUALIFY ROW_NUMBER() OVER (PARTITION BY WI_NAME ORDER BY EXITDATE DESC) = 1) N3 ON N3.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" s="25" t="n"/>
+      <c r="B93" s="25" t="n"/>
+      <c r="C93" s="51" t="n"/>
+      <c r="D93" s="54" t="n"/>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N4 (SELECT WI_NAME, USERNAME FROM STG_FCT_CLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE = 'DataInputerChecker' QUALIFY ROW_NUMBER() OVER (PARTITION BY WI_NAME ORDER BY EXITDATE DESC) = 1) N4 ON N4.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="75" customHeight="1">
+      <c r="A94" s="25" t="n"/>
+      <c r="B94" s="25" t="n"/>
+      <c r="C94" s="51" t="n"/>
+      <c r="D94" s="54" t="n"/>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N5 (SELECT WI_NAME, USERNAME, UNDERWRITERMAKER_USERMAKE FROM STG_FCT_CLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE = 'UnderwriterMaker' QUALIFY ROW_NUMBER() OVER (PARTITION BY WI_NAME ORDER BY EXITDATE DESC) = 1) N5 ON N5.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="75" customHeight="1">
+      <c r="A95" s="25" t="n"/>
+      <c r="B95" s="25" t="n"/>
+      <c r="C95" s="51" t="n"/>
+      <c r="D95" s="54" t="n"/>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N6 (SELECT WI_NAME, USERNAME, UNDERWRITERCHECKER_USERMAKE FROM STG_FCT_CLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE = 'UnderwriterChecker' QUALIFY ROW_NUMBER() OVER (PARTITION BY WI_NAME ORDER BY EXITDATE DESC) = 1) N6 ON N6.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" s="25" t="n"/>
+      <c r="B96" s="25" t="n"/>
+      <c r="C96" s="51" t="n"/>
+      <c r="D96" s="54" t="n"/>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N7 (SELECT WI_NAME, USERNAME FROM STG_FCT_CLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE = 'PhoneVerification' QUALIFY ROW_NUMBER() OVER (PARTITION BY WI_NAME ORDER BY EXITDATE DESC) = 1) N7 ON N7.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" s="25" t="n"/>
+      <c r="B97" s="25" t="n"/>
+      <c r="C97" s="51" t="n"/>
+      <c r="D97" s="54" t="n"/>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N8 (SELECT WI_NAME, USERNAME FROM STG_FCT_CLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE = 'FieldAssessment' QUALIFY ROW_NUMBER() OVER (PARTITION BY WI_NAME ORDER BY EXITDATE DESC) = 1) N8 ON N8.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" s="25" t="n"/>
+      <c r="B98" s="25" t="n"/>
+      <c r="C98" s="51" t="n"/>
+      <c r="D98" s="54" t="n"/>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N9 (SELECT WI_NAME, USERNAME FROM STG_FCT_CLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE = 'CreditApproval' QUALIFY ROW_NUMBER() OVER (PARTITION BY WI_NAME ORDER BY EXITDATE DESC) = 1) N9 ON N9.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" s="25" t="n"/>
+      <c r="B99" s="25" t="n"/>
+      <c r="C99" s="51" t="n"/>
+      <c r="D99" s="54" t="n"/>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N10 (SELECT WI_NAME, USERNAME FROM STG_FCT_CLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE = 'CreditCommittee' QUALIFY ROW_NUMBER() OVER (PARTITION BY WI_NAME ORDER BY EXITDATE DESC) = 1) N10 ON N10.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" s="25" t="n"/>
+      <c r="B100" s="25" t="n"/>
+      <c r="C100" s="51" t="n"/>
+      <c r="D100" s="54" t="n"/>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N11 (SELECT WI_NAME, USERNAME FROM STG_FCT_CLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE = 'HOSupport' QUALIFY ROW_NUMBER() OVER (PARTITION BY WI_NAME ORDER BY EXITDATE DESC) = 1) N11 ON N11.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" s="25" t="n"/>
+      <c r="B101" s="25" t="n"/>
+      <c r="C101" s="51" t="n"/>
+      <c r="D101" s="54" t="n"/>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N12 (SELECT WI_NAME, MAX(EXITDATE) AS LAST_APPROVAL_DATE FROM STG_FCT_CLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE IN ('CreditApproval','CreditCommittee') GROUP BY WI_NAME) N12 ON N12.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="45" customHeight="1">
+      <c r="A102" s="25" t="n"/>
+      <c r="B102" s="25" t="n"/>
+      <c r="C102" s="51" t="n"/>
+      <c r="D102" s="54" t="n"/>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N13 (SELECT WI_NAME, MIN(ENTRYDATE) AS MIN_UWM FROM STG_FCT_CLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE = 'UnderwriterMaker' GROUP BY WI_NAME) N13 ON N13.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" s="25" t="n"/>
+      <c r="B103" s="25" t="n"/>
+      <c r="C103" s="51" t="n"/>
+      <c r="D103" s="54" t="n"/>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N14 (SELECT WI_NAME, MIN(ENTRYDATE) AS MIN_APP FROM STG_FCT_CLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE IN ('CreditApproval','CreditCommittee') GROUP BY WI_NAME) N14 ON N14.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="45" customHeight="1">
+      <c r="A104" s="25" t="n"/>
+      <c r="B104" s="25" t="n"/>
+      <c r="C104" s="51" t="n"/>
+      <c r="D104" s="54" t="n"/>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N15 (SELECT WI_NAME, ENTRYDATE FROM STG_FCT_CLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE = 'CancelRevoke') N15 ON N15.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" s="25" t="n"/>
+      <c r="B105" s="25" t="n"/>
+      <c r="C105" s="51" t="n"/>
+      <c r="D105" s="54" t="n"/>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N16 (SELECT WI_NAME, ENTRYDATE, EXITDATE, REMARKS FROM STG_FCT_CLOS_WORKSTEP_EVENT WHERE EXITDATE IS NOT NULL QUALIFY ROW_NUMBER() OVER (PARTITION BY WI_NAME ORDER BY ENTRYDATE DESC) = 1) N16 ON N16.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" s="25" t="n"/>
+      <c r="B106" s="25" t="n"/>
+      <c r="C106" s="51" t="n"/>
+      <c r="D106" s="54" t="n"/>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N17 (SELECT WI_NAME, APPROVAL_USERMAKE FROM STG_FCT_CLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE IN ('CreditCommittee','CreditApproval') QUALIFY ROW_NUMBER() OVER (PARTITION BY WI_NAME ORDER BY ENTRYDATE DESC) = 1) N17 ON N17.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="25" t="n"/>
+      <c r="B107" s="25" t="n"/>
+      <c r="C107" s="51" t="n"/>
+      <c r="D107" s="54" t="n"/>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN E.WORKSTEP_CODE = F.WORKSTEP_CODE AND E.DECISION_CODE = F.DECISION_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="15" customHeight="1">
+      <c r="A108" s="25" t="n"/>
+      <c r="B108" s="25" t="n"/>
+      <c r="C108" s="51" t="n"/>
+      <c r="D108" s="54" t="n"/>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN PL.PRODUCTLINE_SK = A.PRODUCTLINE_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="15" customHeight="1">
+      <c r="A109" s="25" t="n"/>
+      <c r="B109" s="25" t="n"/>
+      <c r="C109" s="51" t="n"/>
+      <c r="D109" s="54" t="n"/>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN SP.SUB_PRODUCT_SK = A.SUB_PRODUCT_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="15" customHeight="1">
+      <c r="A110" s="25" t="n"/>
+      <c r="B110" s="25" t="n"/>
+      <c r="C110" s="51" t="n"/>
+      <c r="D110" s="54" t="n"/>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN I.DIMENSION_KEY = A.APPLICATION_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="105" customHeight="1">
+      <c r="A111" s="25" t="n"/>
+      <c r="B111" s="25" t="n"/>
+      <c r="C111" s="51" t="n"/>
+      <c r="D111" s="54" t="n"/>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN J ON (CASE WHEN A.CHANGE_REQUEST = 'Change Request' THEN J.PRODUCT_LINE = 'Trường Change Request' ELSE J.PRODUCT_LINE = PL.PRODUCTLINE_NAME END) AND (J.SUB_PRODUCT IS NULL OR J.SUB_PRODUCT = SP.SUB_PRODUCT_NAME) AND J.HAVE_ANY_DEVIATION = I.HAVE_ANY_DEVIATION AND J.FLAG_APP_GRP = CASE WHEN I.APP_GRP IN ('A1','A2','B1','B2') THEN 'CGPD' WHEN I.APP_GRP IN ('BOD','CC','SCC','RCC') THEN 'HDTD' END AND B.CUST_GROUP IN ('NBFI','JSC','FDI','BANK','STR','SOC')</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="105" customHeight="1">
+      <c r="A112" s="25" t="n"/>
+      <c r="B112" s="25" t="n"/>
+      <c r="C112" s="51" t="n"/>
+      <c r="D112" s="54" t="n"/>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN K ON (CASE WHEN A.CHANGE_REQUEST = 'Change Request' THEN K.PRODUCT_LINE = 'Trường Change Request' ELSE K.PRODUCT_LINE = PL.PRODUCTLINE_NAME END) AND (K.SUB_PRODUCT IS NULL OR K.SUB_PRODUCT = SP.SUB_PRODUCT_NAME) AND K.HAVE_ANY_DEVIATION = I.HAVE_ANY_DEVIATION AND K.FLAG_APP_GRP = CASE WHEN I.APP_GRP IN ('A1','A2','B1','B2') THEN 'CGPD' WHEN I.APP_GRP IN ('BOD','CC','SCC','RCC') THEN 'HDTD' END AND B.CUST_GROUP IN ('MSME','SME','USME','C1')</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="75" customHeight="1">
+      <c r="A113" s="25" t="n"/>
+      <c r="B113" s="25" t="n"/>
+      <c r="C113" s="51" t="n"/>
+      <c r="D113" s="54" t="n"/>
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN LP (SELECT WI_NAME, LISTAGG(FULL_NAME, ';') AS LEGAL_REPRESENTATIVE, LISTAGG(ID_NUMBER, ';') AS ADD_ID_REPRESENTATIVE FROM STG_FCT_CLOS_LEGAL_PARTY WHERE OBJ_TYPE = 'Người đại diện theo pháp luật' GROUP BY WI_NAME) LP ON LP.WI_NAME = I.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="15" customHeight="1">
+      <c r="A114" s="25" t="n"/>
+      <c r="B114" s="25" t="n"/>
+      <c r="C114" s="51" t="n"/>
+      <c r="D114" s="54" t="n"/>
+      <c r="E114" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN M.WI_NAME = A.WI_NAME</t>
         </is>
       </c>
     </row>
